--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>编号</t>
   </si>
@@ -35,6 +35,9 @@
     <t>名称</t>
   </si>
   <si>
+    <t>状态</t>
+  </si>
+  <si>
     <t>试算开始日期</t>
   </si>
   <si>
@@ -59,7 +62,10 @@
     <t>历史销量类型</t>
   </si>
   <si>
-    <t>试算吻合度</t>
+    <t>R²吻合度</t>
+  </si>
+  <si>
+    <t>MAPE吻合度</t>
   </si>
   <si>
     <t>备注</t>
@@ -83,6 +89,9 @@
     <t>{.name}</t>
   </si>
   <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
     <t>{.startCalcDate}</t>
   </si>
   <si>
@@ -107,7 +116,10 @@
     <t>{.saleTypeName}</t>
   </si>
   <si>
-    <t>{.similarity}</t>
+    <t>{.r2Score}</t>
+  </si>
+  <si>
+    <t>{.mapeScore}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1311,19 +1323,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="13" max="13" width="22.375" customWidth="1"/>
-    <col min="14" max="14" width="16.375" customWidth="1"/>
-    <col min="15" max="15" width="22.75" customWidth="1"/>
-    <col min="16" max="16" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="12" max="13" width="18.625" customWidth="1"/>
+    <col min="15" max="15" width="22.375" customWidth="1"/>
+    <col min="16" max="16" width="16.375" customWidth="1"/>
+    <col min="17" max="17" width="22.75" customWidth="1"/>
+    <col min="18" max="18" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:24">
+    <row r="1" s="1" customFormat="1" spans="1:26">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1350,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1348,10 +1362,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -1360,75 +1374,87 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>编号</t>
   </si>
@@ -62,10 +62,16 @@
     <t>历史销量类型</t>
   </si>
   <si>
-    <t>R²吻合度</t>
-  </si>
-  <si>
-    <t>MAPE吻合度</t>
+    <t>R²吻合度(日)</t>
+  </si>
+  <si>
+    <t>R²吻合度(月)</t>
+  </si>
+  <si>
+    <t>MAPE吻合度(日)</t>
+  </si>
+  <si>
+    <t>MAPE吻合度(月)</t>
   </si>
   <si>
     <t>备注</t>
@@ -119,7 +125,13 @@
     <t>{.r2Score}</t>
   </si>
   <si>
+    <t>{.monthR2Score}</t>
+  </si>
+  <si>
     <t>{.mapeScore}</t>
+  </si>
+  <si>
+    <t>{.monthMapeScore}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1323,21 +1335,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="16.25" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="15.125" customWidth="1"/>
     <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="13" width="18.625" customWidth="1"/>
-    <col min="15" max="15" width="22.375" customWidth="1"/>
-    <col min="16" max="16" width="16.375" customWidth="1"/>
-    <col min="17" max="17" width="22.75" customWidth="1"/>
-    <col min="18" max="18" width="18.125" customWidth="1"/>
+    <col min="12" max="15" width="18.625" customWidth="1"/>
+    <col min="17" max="17" width="22.375" customWidth="1"/>
+    <col min="18" max="18" width="16.375" customWidth="1"/>
+    <col min="19" max="19" width="22.75" customWidth="1"/>
+    <col min="20" max="20" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:26">
+    <row r="1" s="1" customFormat="1" spans="1:28">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1380,81 +1392,93 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
+      <c r="S1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>编号</t>
   </si>
@@ -35,7 +35,10 @@
     <t>名称</t>
   </si>
   <si>
-    <t>状态</t>
+    <t>任务序号</t>
+  </si>
+  <si>
+    <t>任务状态状态</t>
   </si>
   <si>
     <t>试算开始日期</t>
@@ -1335,21 +1338,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="16.25" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
-    <col min="12" max="15" width="18.625" customWidth="1"/>
-    <col min="17" max="17" width="22.375" customWidth="1"/>
-    <col min="18" max="18" width="16.375" customWidth="1"/>
-    <col min="19" max="19" width="22.75" customWidth="1"/>
-    <col min="20" max="20" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="15.125" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="16" width="18.625" customWidth="1"/>
+    <col min="18" max="18" width="22.375" customWidth="1"/>
+    <col min="19" max="19" width="16.375" customWidth="1"/>
+    <col min="20" max="20" width="22.75" customWidth="1"/>
+    <col min="21" max="21" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" spans="1:29">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1365,7 +1368,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1377,10 +1380,10 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
@@ -1398,7 +1401,7 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -1407,10 +1410,12 @@
       <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
@@ -1418,16 +1423,17 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1479,6 +1485,9 @@
       </c>
       <c r="T2" t="s">
         <v>39</v>
+      </c>
+      <c r="U2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalcList.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>编号</t>
   </si>
@@ -38,7 +38,7 @@
     <t>任务序号</t>
   </si>
   <si>
-    <t>任务状态状态</t>
+    <t>任务状态</t>
   </si>
   <si>
     <t>试算开始日期</t>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.serialNo}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -1436,58 +1439,58 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
